--- a/Pruebas calificadas/COLEGIO EL ENSUEÑO (IED)-902_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO EL ENSUEÑO (IED)-902_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1562,11 +1550,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -1574,7 +1558,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1815,11 +1799,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -1827,7 +1807,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2068,11 +2048,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -2080,7 +2056,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2321,11 +2297,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -2333,7 +2305,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2574,11 +2546,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -2586,7 +2554,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2827,11 +2795,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -2839,7 +2803,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3080,11 +3044,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -3092,7 +3052,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3333,11 +3293,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -3345,7 +3301,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3586,11 +3542,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -3598,7 +3550,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3839,11 +3791,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -3851,7 +3799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4092,11 +4040,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -4104,7 +4048,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4345,11 +4289,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -4357,7 +4297,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4594,11 +4534,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -4606,7 +4542,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4847,11 +4783,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -4859,7 +4791,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5100,11 +5032,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -5112,7 +5040,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5349,11 +5277,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -5361,7 +5285,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5602,11 +5526,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -5614,7 +5534,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5847,11 +5767,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -5859,7 +5775,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6100,11 +6016,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -6112,7 +6024,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6353,11 +6265,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -6365,7 +6273,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6606,11 +6514,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -6618,7 +6522,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6859,11 +6763,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -6871,7 +6771,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7112,11 +7012,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -7124,7 +7020,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7361,11 +7257,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -7373,7 +7265,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7614,11 +7506,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -7626,7 +7514,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7867,11 +7755,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -7879,7 +7763,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8116,11 +8000,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -8128,7 +8008,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8369,11 +8249,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -8381,7 +8257,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8614,11 +8490,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -8626,7 +8498,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8863,11 +8735,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -8875,7 +8743,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9112,11 +8980,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -9124,7 +8988,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9365,11 +9229,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -9377,7 +9237,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9614,11 +9474,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -9626,7 +9482,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9867,11 +9723,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -9879,7 +9731,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10120,11 +9972,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -10132,7 +9980,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10373,11 +10221,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -10385,7 +10229,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10626,11 +10470,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -10638,7 +10478,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10879,11 +10719,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -10891,7 +10727,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11132,11 +10968,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -11144,7 +10976,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11385,11 +11217,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -11397,7 +11225,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11638,11 +11466,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -11650,7 +11474,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11891,11 +11715,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -11903,7 +11723,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12144,11 +11964,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -12156,7 +11972,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12397,11 +12213,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -12409,7 +12221,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12650,11 +12462,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -12662,7 +12470,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12903,11 +12711,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -12915,7 +12719,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13156,11 +12960,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -13168,7 +12968,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13409,11 +13209,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -13421,7 +13217,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13662,11 +13458,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -13674,7 +13466,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13915,11 +13707,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -13927,7 +13715,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14168,11 +13956,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -14180,7 +13964,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14421,11 +14205,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -14433,7 +14213,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14674,11 +14454,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -14686,7 +14462,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14927,11 +14703,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -14939,7 +14711,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15180,11 +14952,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -15192,7 +14960,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15433,11 +15201,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -15445,7 +15209,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15686,11 +15450,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -15698,7 +15458,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15939,11 +15699,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -15951,7 +15707,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16192,11 +15948,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -16204,7 +15956,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16445,11 +16197,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -16457,7 +16205,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16698,11 +16446,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -16710,7 +16454,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16951,11 +16695,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -16963,7 +16703,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17204,11 +16944,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -17216,7 +16952,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17457,11 +17193,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -17469,7 +17201,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17710,11 +17442,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -17722,7 +17450,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
